--- a/data/raw/cells/Table S1-Patient information and follow-up data.xlsx
+++ b/data/raw/cells/Table S1-Patient information and follow-up data.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Lab\R\Osteo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\parsh\Downloads\ProtML\data\raw\cells\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B84CA0E-CFFF-49EF-900C-2E3B30854BA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="7785" windowHeight="6990"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Osteosarcoma _2022" sheetId="1" r:id="rId1"/>
@@ -24,9 +25,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="89">
   <si>
-    <t>Patient_Code</t>
-  </si>
-  <si>
     <t>Age</t>
   </si>
   <si>
@@ -289,12 +287,15 @@
   </si>
   <si>
     <t>CCHE_306</t>
+  </si>
+  <si>
+    <t>Patient_ID</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1095,129 +1096,129 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:X34"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="4" max="4" width="17" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
       <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" t="s">
-        <v>23</v>
-      </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B2">
         <v>4.8</v>
       </c>
       <c r="C2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D2" s="1">
         <v>40902</v>
       </c>
       <c r="E2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G2">
         <v>435.8</v>
       </c>
       <c r="H2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L2" t="s">
+        <v>29</v>
+      </c>
+      <c r="M2" t="s">
         <v>30</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>31</v>
-      </c>
-      <c r="N2" t="s">
-        <v>32</v>
       </c>
       <c r="O2">
         <v>1</v>
@@ -1226,13 +1227,13 @@
         <v>40955</v>
       </c>
       <c r="Q2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="R2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="S2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="T2">
         <v>1</v>
@@ -1250,48 +1251,48 @@
         <v>3.68</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B3">
         <v>6.25</v>
       </c>
       <c r="C3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D3" s="1">
         <v>41952</v>
       </c>
       <c r="E3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G3">
         <v>56.6</v>
       </c>
       <c r="H3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M3" t="s">
         <v>30</v>
       </c>
-      <c r="M3" t="s">
+      <c r="N3" t="s">
         <v>31</v>
-      </c>
-      <c r="N3" t="s">
-        <v>32</v>
       </c>
       <c r="O3">
         <v>1</v>
@@ -1300,13 +1301,13 @@
         <v>42162</v>
       </c>
       <c r="Q3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="S3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="T3">
         <v>1</v>
@@ -1324,48 +1325,48 @@
         <v>15.43</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B4">
         <v>6.62</v>
       </c>
       <c r="C4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D4" s="1">
         <v>41263</v>
       </c>
       <c r="E4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G4">
         <v>190</v>
       </c>
       <c r="H4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="M4" t="s">
+        <v>30</v>
+      </c>
+      <c r="N4" t="s">
         <v>31</v>
-      </c>
-      <c r="N4" t="s">
-        <v>32</v>
       </c>
       <c r="O4">
         <v>1</v>
@@ -1374,13 +1375,13 @@
         <v>41609</v>
       </c>
       <c r="Q4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="R4" t="s">
+        <v>33</v>
+      </c>
+      <c r="S4" t="s">
         <v>34</v>
-      </c>
-      <c r="S4" t="s">
-        <v>35</v>
       </c>
       <c r="T4">
         <v>1</v>
@@ -1398,48 +1399,48 @@
         <v>16.12</v>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B5">
         <v>6.67</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D5" s="1">
         <v>39294</v>
       </c>
       <c r="E5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G5">
         <v>100</v>
       </c>
       <c r="H5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J5" t="s">
         <v>28</v>
       </c>
-      <c r="J5" t="s">
+      <c r="K5" t="s">
+        <v>26</v>
+      </c>
+      <c r="L5" t="s">
         <v>29</v>
       </c>
-      <c r="K5" t="s">
-        <v>27</v>
-      </c>
-      <c r="L5" t="s">
+      <c r="M5" t="s">
         <v>30</v>
       </c>
-      <c r="M5" t="s">
+      <c r="N5" t="s">
         <v>31</v>
-      </c>
-      <c r="N5" t="s">
-        <v>32</v>
       </c>
       <c r="O5">
         <v>1</v>
@@ -1448,13 +1449,13 @@
         <v>39999</v>
       </c>
       <c r="Q5" t="s">
+        <v>32</v>
+      </c>
+      <c r="R5" t="s">
         <v>33</v>
       </c>
-      <c r="R5" t="s">
+      <c r="S5" t="s">
         <v>34</v>
-      </c>
-      <c r="S5" t="s">
-        <v>35</v>
       </c>
       <c r="T5">
         <v>1</v>
@@ -1472,60 +1473,60 @@
         <v>27.01</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B6">
         <v>7.19</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D6" s="1">
         <v>41149</v>
       </c>
       <c r="E6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G6">
         <v>240.52</v>
       </c>
       <c r="H6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="M6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="Q6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="S6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -1540,48 +1541,48 @@
         <v>80.86</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B7">
         <v>7.24</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D7" s="1">
         <v>41479</v>
       </c>
       <c r="E7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G7">
         <v>329.9</v>
       </c>
       <c r="H7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L7" t="s">
+        <v>29</v>
+      </c>
+      <c r="M7" t="s">
         <v>30</v>
       </c>
-      <c r="M7" t="s">
+      <c r="N7" t="s">
         <v>31</v>
-      </c>
-      <c r="N7" t="s">
-        <v>32</v>
       </c>
       <c r="O7">
         <v>1</v>
@@ -1590,13 +1591,13 @@
         <v>41708</v>
       </c>
       <c r="Q7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="S7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="T7">
         <v>1</v>
@@ -1614,48 +1615,48 @@
         <v>25.46</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B8">
         <v>8.57</v>
       </c>
       <c r="C8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D8" s="1">
         <v>40888</v>
       </c>
       <c r="E8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G8">
         <v>152.69999999999999</v>
       </c>
       <c r="H8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L8" t="s">
+        <v>29</v>
+      </c>
+      <c r="M8" t="s">
         <v>30</v>
       </c>
-      <c r="M8" t="s">
+      <c r="N8" t="s">
         <v>31</v>
-      </c>
-      <c r="N8" t="s">
-        <v>32</v>
       </c>
       <c r="O8">
         <v>1</v>
@@ -1664,13 +1665,13 @@
         <v>41192</v>
       </c>
       <c r="Q8" t="s">
+        <v>32</v>
+      </c>
+      <c r="R8" t="s">
         <v>33</v>
       </c>
-      <c r="R8" t="s">
+      <c r="S8" t="s">
         <v>34</v>
-      </c>
-      <c r="S8" t="s">
-        <v>35</v>
       </c>
       <c r="T8">
         <v>1</v>
@@ -1688,60 +1689,60 @@
         <v>15.36</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B9">
         <v>8.85</v>
       </c>
       <c r="C9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D9" s="1">
         <v>40398</v>
       </c>
       <c r="E9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G9">
         <v>50.8</v>
       </c>
       <c r="H9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O9">
         <v>0</v>
       </c>
       <c r="Q9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="S9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="T9">
         <v>0</v>
@@ -1756,48 +1757,48 @@
         <v>102.6</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B10">
         <v>9.5399999999999991</v>
       </c>
       <c r="C10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D10" s="1">
         <v>40517</v>
       </c>
       <c r="E10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G10">
         <v>278.8</v>
       </c>
       <c r="H10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L10" t="s">
+        <v>29</v>
+      </c>
+      <c r="M10" t="s">
         <v>30</v>
       </c>
-      <c r="M10" t="s">
+      <c r="N10" t="s">
         <v>31</v>
-      </c>
-      <c r="N10" t="s">
-        <v>32</v>
       </c>
       <c r="O10">
         <v>1</v>
@@ -1806,13 +1807,13 @@
         <v>40947</v>
       </c>
       <c r="Q10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="R10" t="s">
+        <v>33</v>
+      </c>
+      <c r="S10" t="s">
         <v>34</v>
-      </c>
-      <c r="S10" t="s">
-        <v>35</v>
       </c>
       <c r="T10">
         <v>1</v>
@@ -1830,48 +1831,48 @@
         <v>19.739999999999998</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B11">
         <v>10.57</v>
       </c>
       <c r="C11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D11" s="1">
         <v>42143</v>
       </c>
       <c r="E11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L11" t="s">
+        <v>29</v>
+      </c>
+      <c r="M11" t="s">
         <v>30</v>
       </c>
-      <c r="M11" t="s">
+      <c r="N11" t="s">
         <v>31</v>
-      </c>
-      <c r="N11" t="s">
-        <v>32</v>
       </c>
       <c r="O11">
         <v>1</v>
@@ -1880,13 +1881,13 @@
         <v>42323</v>
       </c>
       <c r="Q11" t="s">
+        <v>32</v>
+      </c>
+      <c r="R11" t="s">
         <v>33</v>
       </c>
-      <c r="R11" t="s">
+      <c r="S11" t="s">
         <v>34</v>
-      </c>
-      <c r="S11" t="s">
-        <v>35</v>
       </c>
       <c r="T11">
         <v>1</v>
@@ -1904,60 +1905,60 @@
         <v>8.36</v>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B12">
         <v>11.74</v>
       </c>
       <c r="C12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D12" s="1">
         <v>41891</v>
       </c>
       <c r="E12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G12">
         <v>177.5</v>
       </c>
       <c r="H12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I12" t="s">
+        <v>27</v>
+      </c>
+      <c r="J12" t="s">
         <v>28</v>
       </c>
-      <c r="J12" t="s">
+      <c r="K12" t="s">
+        <v>26</v>
+      </c>
+      <c r="L12" t="s">
         <v>29</v>
       </c>
-      <c r="K12" t="s">
-        <v>27</v>
-      </c>
-      <c r="L12" t="s">
-        <v>30</v>
-      </c>
       <c r="M12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="N12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O12">
         <v>0</v>
       </c>
       <c r="Q12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="S12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="T12">
         <v>0</v>
@@ -1972,48 +1973,48 @@
         <v>55.43</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B13">
         <v>11.96</v>
       </c>
       <c r="C13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D13" s="1">
         <v>41021</v>
       </c>
       <c r="E13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G13">
         <v>672</v>
       </c>
       <c r="H13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J13" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L13" t="s">
+        <v>29</v>
+      </c>
+      <c r="M13" t="s">
         <v>30</v>
       </c>
-      <c r="M13" t="s">
+      <c r="N13" t="s">
         <v>31</v>
-      </c>
-      <c r="N13" t="s">
-        <v>32</v>
       </c>
       <c r="O13">
         <v>1</v>
@@ -2022,13 +2023,13 @@
         <v>41101</v>
       </c>
       <c r="Q13" t="s">
+        <v>32</v>
+      </c>
+      <c r="R13" t="s">
         <v>33</v>
       </c>
-      <c r="R13" t="s">
+      <c r="S13" t="s">
         <v>34</v>
-      </c>
-      <c r="S13" t="s">
-        <v>35</v>
       </c>
       <c r="T13">
         <v>1</v>
@@ -2046,48 +2047,48 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B14">
         <v>12.31</v>
       </c>
       <c r="C14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D14" s="1">
         <v>40973</v>
       </c>
       <c r="E14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G14">
         <v>1769.9</v>
       </c>
       <c r="H14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I14" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J14" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L14" t="s">
+        <v>29</v>
+      </c>
+      <c r="M14" t="s">
         <v>30</v>
       </c>
-      <c r="M14" t="s">
+      <c r="N14" t="s">
         <v>31</v>
-      </c>
-      <c r="N14" t="s">
-        <v>32</v>
       </c>
       <c r="O14">
         <v>1</v>
@@ -2096,13 +2097,13 @@
         <v>42148</v>
       </c>
       <c r="Q14" t="s">
+        <v>32</v>
+      </c>
+      <c r="R14" t="s">
         <v>33</v>
       </c>
-      <c r="R14" t="s">
-        <v>34</v>
-      </c>
       <c r="S14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="T14">
         <v>0</v>
@@ -2117,60 +2118,60 @@
         <v>84.34</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B15">
         <v>12.48</v>
       </c>
       <c r="C15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D15" s="1">
         <v>40206</v>
       </c>
       <c r="E15" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G15">
         <v>316.10000000000002</v>
       </c>
       <c r="H15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I15" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L15" t="s">
+        <v>29</v>
+      </c>
+      <c r="M15" t="s">
         <v>30</v>
       </c>
-      <c r="M15" t="s">
-        <v>31</v>
-      </c>
       <c r="N15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O15">
         <v>0</v>
       </c>
       <c r="Q15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="S15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="T15">
         <v>0</v>
@@ -2185,60 +2186,60 @@
         <v>109.7</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B16">
         <v>12.75</v>
       </c>
       <c r="C16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D16" s="1">
         <v>42059</v>
       </c>
       <c r="E16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G16">
         <v>143.6</v>
       </c>
       <c r="H16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L16" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="M16" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O16">
         <v>0</v>
       </c>
       <c r="Q16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="S16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="T16">
         <v>0</v>
@@ -2253,48 +2254,48 @@
         <v>50.82</v>
       </c>
     </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B17">
         <v>13.26</v>
       </c>
       <c r="C17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D17" s="1">
         <v>41777</v>
       </c>
       <c r="E17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G17">
         <v>1166.9000000000001</v>
       </c>
       <c r="H17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I17" t="s">
+        <v>27</v>
+      </c>
+      <c r="J17" t="s">
         <v>28</v>
       </c>
-      <c r="J17" t="s">
+      <c r="K17" t="s">
+        <v>26</v>
+      </c>
+      <c r="L17" t="s">
         <v>29</v>
       </c>
-      <c r="K17" t="s">
-        <v>27</v>
-      </c>
-      <c r="L17" t="s">
+      <c r="M17" t="s">
         <v>30</v>
       </c>
-      <c r="M17" t="s">
+      <c r="N17" t="s">
         <v>31</v>
-      </c>
-      <c r="N17" t="s">
-        <v>32</v>
       </c>
       <c r="O17">
         <v>1</v>
@@ -2303,13 +2304,13 @@
         <v>42288</v>
       </c>
       <c r="Q17" t="s">
+        <v>32</v>
+      </c>
+      <c r="R17" t="s">
         <v>33</v>
       </c>
-      <c r="R17" t="s">
+      <c r="S17" t="s">
         <v>34</v>
-      </c>
-      <c r="S17" t="s">
-        <v>35</v>
       </c>
       <c r="T17">
         <v>1</v>
@@ -2327,60 +2328,60 @@
         <v>25.86</v>
       </c>
     </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B18">
         <v>13.32</v>
       </c>
       <c r="C18" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D18" s="1">
         <v>41119</v>
       </c>
       <c r="E18" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G18">
         <v>407.9</v>
       </c>
       <c r="H18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J18" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L18" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="M18" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O18">
         <v>0</v>
       </c>
       <c r="Q18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="S18" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="T18">
         <v>0</v>
@@ -2395,48 +2396,48 @@
         <v>80.459999999999994</v>
       </c>
     </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B19">
         <v>13.32</v>
       </c>
       <c r="C19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D19" s="1">
         <v>41730</v>
       </c>
       <c r="E19" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G19">
         <v>2565.2399999999998</v>
       </c>
       <c r="H19" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I19" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J19" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L19" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M19" t="s">
+        <v>30</v>
+      </c>
+      <c r="N19" t="s">
         <v>31</v>
-      </c>
-      <c r="N19" t="s">
-        <v>32</v>
       </c>
       <c r="O19">
         <v>1</v>
@@ -2445,13 +2446,13 @@
         <v>41828</v>
       </c>
       <c r="Q19" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="R19" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="S19" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="T19">
         <v>1</v>
@@ -2469,60 +2470,60 @@
         <v>5.82</v>
       </c>
     </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B20">
         <v>14.31</v>
       </c>
       <c r="C20" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D20" s="1">
         <v>41694</v>
       </c>
       <c r="E20" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F20" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G20">
         <v>268.89999999999998</v>
       </c>
       <c r="H20" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I20" t="s">
+        <v>27</v>
+      </c>
+      <c r="J20" t="s">
         <v>28</v>
       </c>
-      <c r="J20" t="s">
+      <c r="K20" t="s">
+        <v>26</v>
+      </c>
+      <c r="L20" t="s">
         <v>29</v>
       </c>
-      <c r="K20" t="s">
-        <v>27</v>
-      </c>
-      <c r="L20" t="s">
+      <c r="M20" t="s">
         <v>30</v>
       </c>
-      <c r="M20" t="s">
-        <v>31</v>
-      </c>
       <c r="N20" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O20">
         <v>0</v>
       </c>
       <c r="Q20" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R20" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="S20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="T20">
         <v>0</v>
@@ -2537,60 +2538,60 @@
         <v>61.22</v>
       </c>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B21">
         <v>14.84</v>
       </c>
       <c r="C21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D21" s="1">
         <v>40615</v>
       </c>
       <c r="E21" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G21">
         <v>274.5</v>
       </c>
       <c r="H21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J21" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L21" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="M21" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O21">
         <v>0</v>
       </c>
       <c r="Q21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="S21" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="T21">
         <v>0</v>
@@ -2605,48 +2606,48 @@
         <v>102.24</v>
       </c>
     </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B22">
         <v>15.64</v>
       </c>
       <c r="C22" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D22" s="1">
         <v>41337</v>
       </c>
       <c r="E22" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F22" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G22">
         <v>605.70000000000005</v>
       </c>
       <c r="H22" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I22" t="s">
+        <v>27</v>
+      </c>
+      <c r="J22" t="s">
         <v>28</v>
       </c>
-      <c r="J22" t="s">
+      <c r="K22" t="s">
+        <v>26</v>
+      </c>
+      <c r="L22" t="s">
         <v>29</v>
       </c>
-      <c r="K22" t="s">
-        <v>27</v>
-      </c>
-      <c r="L22" t="s">
+      <c r="M22" t="s">
         <v>30</v>
       </c>
-      <c r="M22" t="s">
+      <c r="N22" t="s">
         <v>31</v>
-      </c>
-      <c r="N22" t="s">
-        <v>32</v>
       </c>
       <c r="O22">
         <v>1</v>
@@ -2655,13 +2656,13 @@
         <v>41637</v>
       </c>
       <c r="Q22" t="s">
+        <v>32</v>
+      </c>
+      <c r="R22" t="s">
         <v>33</v>
       </c>
-      <c r="R22" t="s">
+      <c r="S22" t="s">
         <v>34</v>
-      </c>
-      <c r="S22" t="s">
-        <v>35</v>
       </c>
       <c r="T22">
         <v>1</v>
@@ -2679,48 +2680,48 @@
         <v>11.84</v>
       </c>
     </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B23">
         <v>15.64</v>
       </c>
       <c r="C23" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D23" s="1">
         <v>41415</v>
       </c>
       <c r="E23" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F23" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G23">
         <v>4799.3999999999996</v>
       </c>
       <c r="H23" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I23" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J23" t="s">
+        <v>28</v>
+      </c>
+      <c r="K23" t="s">
+        <v>26</v>
+      </c>
+      <c r="L23" t="s">
         <v>29</v>
       </c>
-      <c r="K23" t="s">
-        <v>27</v>
-      </c>
-      <c r="L23" t="s">
+      <c r="M23" t="s">
         <v>30</v>
       </c>
-      <c r="M23" t="s">
+      <c r="N23" t="s">
         <v>31</v>
-      </c>
-      <c r="N23" t="s">
-        <v>32</v>
       </c>
       <c r="O23">
         <v>1</v>
@@ -2729,13 +2730,13 @@
         <v>41572</v>
       </c>
       <c r="Q23" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="R23" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="S23" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="T23">
         <v>1</v>
@@ -2753,60 +2754,60 @@
         <v>6.05</v>
       </c>
     </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B24">
         <v>15.83</v>
       </c>
       <c r="C24" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D24" s="1">
         <v>42094</v>
       </c>
       <c r="E24" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F24" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G24">
         <v>261.8</v>
       </c>
       <c r="H24" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I24" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J24" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K24" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L24" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="M24" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N24" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O24">
         <v>0</v>
       </c>
       <c r="Q24" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R24" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="S24" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="T24">
         <v>0</v>
@@ -2821,60 +2822,60 @@
         <v>52.04</v>
       </c>
     </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B25">
         <v>15.92</v>
       </c>
       <c r="C25" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D25" s="1">
         <v>40576</v>
       </c>
       <c r="E25" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F25" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G25">
         <v>47.7</v>
       </c>
       <c r="H25" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J25" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K25" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L25" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M25" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N25" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O25">
         <v>0</v>
       </c>
       <c r="Q25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="S25" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="T25">
         <v>0</v>
@@ -2889,60 +2890,60 @@
         <v>96.68</v>
       </c>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B26">
         <v>16.05</v>
       </c>
       <c r="C26" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D26" s="1">
         <v>39785</v>
       </c>
       <c r="E26" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G26">
         <v>24.96</v>
       </c>
       <c r="H26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I26" t="s">
+        <v>27</v>
+      </c>
+      <c r="J26" t="s">
         <v>28</v>
       </c>
-      <c r="J26" t="s">
+      <c r="K26" t="s">
+        <v>26</v>
+      </c>
+      <c r="L26" t="s">
         <v>29</v>
       </c>
-      <c r="K26" t="s">
-        <v>27</v>
-      </c>
-      <c r="L26" t="s">
+      <c r="M26" t="s">
         <v>30</v>
       </c>
-      <c r="M26" t="s">
-        <v>31</v>
-      </c>
       <c r="N26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O26">
         <v>0</v>
       </c>
       <c r="Q26" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R26" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="S26" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="T26">
         <v>0</v>
@@ -2957,48 +2958,48 @@
         <v>124.05</v>
       </c>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B27">
         <v>16.14</v>
       </c>
       <c r="C27" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D27" s="1">
         <v>41340</v>
       </c>
       <c r="E27" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F27" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G27">
         <v>273.89999999999998</v>
       </c>
       <c r="H27" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I27" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J27" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K27" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L27" t="s">
+        <v>29</v>
+      </c>
+      <c r="M27" t="s">
         <v>30</v>
       </c>
-      <c r="M27" t="s">
+      <c r="N27" t="s">
         <v>31</v>
-      </c>
-      <c r="N27" t="s">
-        <v>32</v>
       </c>
       <c r="O27">
         <v>1</v>
@@ -3007,13 +3008,13 @@
         <v>41568</v>
       </c>
       <c r="Q27" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R27" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="S27" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="T27">
         <v>1</v>
@@ -3031,48 +3032,48 @@
         <v>10.89</v>
       </c>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B28">
         <v>16.559999999999999</v>
       </c>
       <c r="C28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D28" s="1">
         <v>41637</v>
       </c>
       <c r="E28" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F28" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G28">
         <v>2995</v>
       </c>
       <c r="H28" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I28" t="s">
+        <v>27</v>
+      </c>
+      <c r="J28" t="s">
         <v>28</v>
       </c>
-      <c r="J28" t="s">
+      <c r="K28" t="s">
+        <v>26</v>
+      </c>
+      <c r="L28" t="s">
         <v>29</v>
       </c>
-      <c r="K28" t="s">
-        <v>27</v>
-      </c>
-      <c r="L28" t="s">
+      <c r="M28" t="s">
         <v>30</v>
       </c>
-      <c r="M28" t="s">
+      <c r="N28" t="s">
         <v>31</v>
-      </c>
-      <c r="N28" t="s">
-        <v>32</v>
       </c>
       <c r="O28">
         <v>1</v>
@@ -3081,13 +3082,13 @@
         <v>41758</v>
       </c>
       <c r="Q28" t="s">
+        <v>32</v>
+      </c>
+      <c r="R28" t="s">
         <v>33</v>
       </c>
-      <c r="R28" t="s">
+      <c r="S28" t="s">
         <v>34</v>
-      </c>
-      <c r="S28" t="s">
-        <v>35</v>
       </c>
       <c r="T28">
         <v>1</v>
@@ -3105,48 +3106,48 @@
         <v>8.09</v>
       </c>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B29">
         <v>17.09</v>
       </c>
       <c r="C29" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D29" s="1">
         <v>41386</v>
       </c>
       <c r="E29" t="s">
+        <v>68</v>
+      </c>
+      <c r="F29" t="s">
+        <v>26</v>
+      </c>
+      <c r="G29" t="s">
         <v>69</v>
       </c>
-      <c r="F29" t="s">
-        <v>27</v>
-      </c>
-      <c r="G29" t="s">
-        <v>70</v>
-      </c>
       <c r="H29" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I29" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J29" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K29" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L29" t="s">
+        <v>29</v>
+      </c>
+      <c r="M29" t="s">
         <v>30</v>
       </c>
-      <c r="M29" t="s">
+      <c r="N29" t="s">
         <v>31</v>
-      </c>
-      <c r="N29" t="s">
-        <v>32</v>
       </c>
       <c r="O29">
         <v>1</v>
@@ -3155,13 +3156,13 @@
         <v>42037</v>
       </c>
       <c r="Q29" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R29" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="S29" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="T29">
         <v>1</v>
@@ -3179,48 +3180,48 @@
         <v>37.11</v>
       </c>
     </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B30">
         <v>17.329999999999998</v>
       </c>
       <c r="C30" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D30" s="1">
         <v>40545</v>
       </c>
       <c r="E30" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F30" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G30">
         <v>121.6</v>
       </c>
       <c r="H30" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I30" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J30" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K30" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L30" t="s">
+        <v>29</v>
+      </c>
+      <c r="M30" t="s">
         <v>30</v>
       </c>
-      <c r="M30" t="s">
+      <c r="N30" t="s">
         <v>31</v>
-      </c>
-      <c r="N30" t="s">
-        <v>32</v>
       </c>
       <c r="O30">
         <v>1</v>
@@ -3229,13 +3230,13 @@
         <v>40897</v>
       </c>
       <c r="Q30" t="s">
+        <v>32</v>
+      </c>
+      <c r="R30" t="s">
         <v>33</v>
       </c>
-      <c r="R30" t="s">
+      <c r="S30" t="s">
         <v>34</v>
-      </c>
-      <c r="S30" t="s">
-        <v>35</v>
       </c>
       <c r="T30">
         <v>1</v>
@@ -3253,48 +3254,48 @@
         <v>13.78</v>
       </c>
     </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B31">
         <v>17.329999999999998</v>
       </c>
       <c r="C31" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D31" s="1">
         <v>42106</v>
       </c>
       <c r="E31" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F31" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G31">
         <v>449.3</v>
       </c>
       <c r="H31" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I31" t="s">
+        <v>40</v>
+      </c>
+      <c r="J31" t="s">
         <v>41</v>
       </c>
-      <c r="J31" t="s">
-        <v>42</v>
-      </c>
       <c r="K31" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L31" t="s">
+        <v>29</v>
+      </c>
+      <c r="M31" t="s">
         <v>30</v>
       </c>
-      <c r="M31" t="s">
+      <c r="N31" t="s">
         <v>31</v>
-      </c>
-      <c r="N31" t="s">
-        <v>32</v>
       </c>
       <c r="O31">
         <v>1</v>
@@ -3303,13 +3304,13 @@
         <v>42632</v>
       </c>
       <c r="Q31" t="s">
+        <v>32</v>
+      </c>
+      <c r="R31" t="s">
         <v>33</v>
       </c>
-      <c r="R31" t="s">
+      <c r="S31" t="s">
         <v>34</v>
-      </c>
-      <c r="S31" t="s">
-        <v>35</v>
       </c>
       <c r="T31">
         <v>1</v>
@@ -3327,48 +3328,48 @@
         <v>39.14</v>
       </c>
     </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B32">
         <v>17.59</v>
       </c>
       <c r="C32" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D32" s="1">
         <v>42106</v>
       </c>
       <c r="E32" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F32" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G32">
         <v>12.3</v>
       </c>
       <c r="H32" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I32" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J32" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K32" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L32" t="s">
+        <v>29</v>
+      </c>
+      <c r="M32" t="s">
         <v>30</v>
       </c>
-      <c r="M32" t="s">
+      <c r="N32" t="s">
         <v>31</v>
-      </c>
-      <c r="N32" t="s">
-        <v>32</v>
       </c>
       <c r="O32">
         <v>1</v>
@@ -3377,13 +3378,13 @@
         <v>42600</v>
       </c>
       <c r="Q32" t="s">
+        <v>32</v>
+      </c>
+      <c r="R32" t="s">
         <v>33</v>
       </c>
-      <c r="R32" t="s">
+      <c r="S32" t="s">
         <v>34</v>
-      </c>
-      <c r="S32" t="s">
-        <v>35</v>
       </c>
       <c r="T32">
         <v>1</v>
@@ -3401,48 +3402,48 @@
         <v>34.14</v>
       </c>
     </row>
-    <row r="33" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B33">
         <v>17.89</v>
       </c>
       <c r="C33" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D33" s="1">
         <v>40141</v>
       </c>
       <c r="E33" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F33" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G33">
         <v>206</v>
       </c>
       <c r="H33" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I33" t="s">
+        <v>40</v>
+      </c>
+      <c r="J33" t="s">
         <v>41</v>
       </c>
-      <c r="J33" t="s">
-        <v>42</v>
-      </c>
       <c r="K33" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L33" t="s">
+        <v>29</v>
+      </c>
+      <c r="M33" t="s">
         <v>30</v>
       </c>
-      <c r="M33" t="s">
+      <c r="N33" t="s">
         <v>31</v>
-      </c>
-      <c r="N33" t="s">
-        <v>32</v>
       </c>
       <c r="O33">
         <v>1</v>
@@ -3451,13 +3452,13 @@
         <v>40751</v>
       </c>
       <c r="Q33" t="s">
+        <v>32</v>
+      </c>
+      <c r="R33" t="s">
         <v>33</v>
       </c>
-      <c r="R33" t="s">
-        <v>34</v>
-      </c>
       <c r="S33" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="T33">
         <v>0</v>
@@ -3472,60 +3473,60 @@
         <v>115.2</v>
       </c>
     </row>
-    <row r="34" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B34">
         <v>18.3</v>
       </c>
       <c r="C34" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D34" s="1">
         <v>40510</v>
       </c>
       <c r="E34" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F34" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G34">
         <v>108.7</v>
       </c>
       <c r="H34" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I34" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J34" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K34" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L34" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="M34" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N34" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O34">
         <v>0</v>
       </c>
       <c r="Q34" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R34" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="S34" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="T34">
         <v>0</v>
